--- a/mygui_docking/Project1/Project1/data/JY61P_data.xlsx
+++ b/mygui_docking/Project1/Project1/data/JY61P_data.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10812"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Troldal/Development/bin2c/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mxnkilmt\Documents\GitHub\ZJU_Oil\mygui_docking\Project1\Project1\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AC33A6FB-1603-2641-A40F-B7C7F2B0E698}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A143947-FD08-4E38-9834-6C32946C65EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2780" yWindow="1560" windowWidth="28040" windowHeight="17440" xr2:uid="{FF49B81A-127A-B44C-A44B-FF0F3EF8FCF9}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="24196" windowHeight="14476" xr2:uid="{FF49B81A-127A-B44C-A44B-FF0F3EF8FCF9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$K$151</definedName>
+  </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -33,10 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <si>
-    <t/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="36">
   <si>
     <t>Time</t>
   </si>
@@ -150,14 +150,19 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts>
-	</numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -185,7 +190,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -201,7 +206,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -497,53 +502,54 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{049FB1B4-2A61-4643-8816-8B76EC36FD4B}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:K151"/>
+  <sheetFormatPr defaultColWidth="10.8203125" defaultRowHeight="15" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="K1" t="s">
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>12</v>
       </c>
-      <c r="B2" t="s">
-        <v>13</v>
-      </c>
       <c r="C2">
-        <v>0.03076171875</v>
+        <v>3.076171875E-2</v>
       </c>
       <c r="D2">
         <v>0.626953125</v>
@@ -570,15 +576,15 @@
         <v>0.230712890625</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C3">
-        <v>0.03271484375</v>
+        <v>3.271484375E-2</v>
       </c>
       <c r="D3">
         <v>0.6748046875</v>
@@ -602,18 +608,18 @@
         <v>-1.82373046875</v>
       </c>
       <c r="K3">
-        <v>0.0054931640625</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>5.4931640625E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C4">
-        <v>0.0087890625</v>
+        <v>8.7890625E-3</v>
       </c>
       <c r="D4">
         <v>0.5888671875</v>
@@ -640,15 +646,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C5">
-        <v>0.0087890625</v>
+        <v>8.7890625E-3</v>
       </c>
       <c r="D5">
         <v>0.5888671875</v>
@@ -675,15 +681,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C6">
-        <v>0.00146484375</v>
+        <v>1.46484375E-3</v>
       </c>
       <c r="D6">
         <v>0.484375</v>
@@ -707,18 +713,18 @@
         <v>-0.1373291015625</v>
       </c>
       <c r="K6">
-        <v>0.010986328125</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>1.0986328125E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C7">
-        <v>0.00146484375</v>
+        <v>1.46484375E-3</v>
       </c>
       <c r="D7">
         <v>0.484375</v>
@@ -742,18 +748,18 @@
         <v>-0.1373291015625</v>
       </c>
       <c r="K7">
-        <v>0.010986328125</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>1.0986328125E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C8">
-        <v>0.001953125</v>
+        <v>1.953125E-3</v>
       </c>
       <c r="D8">
         <v>0.20947265625</v>
@@ -780,18 +786,18 @@
         <v>-0.252685546875</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C9">
-        <v>0.01806640625</v>
+        <v>1.806640625E-2</v>
       </c>
       <c r="D9">
-        <v>0.083984375</v>
+        <v>8.3984375E-2</v>
       </c>
       <c r="E9">
         <v>0.9912109375</v>
@@ -815,18 +821,18 @@
         <v>0.582275390625</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C10">
-        <v>-0.0302734375</v>
+        <v>-3.02734375E-2</v>
       </c>
       <c r="D10">
-        <v>0.0107421875</v>
+        <v>1.07421875E-2</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -850,15 +856,15 @@
         <v>0.2032470703125</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C11">
-        <v>0.00537109375</v>
+        <v>5.37109375E-3</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -876,24 +882,24 @@
         <v>0</v>
       </c>
       <c r="I11">
-        <v>-0.010986328125</v>
+        <v>-1.0986328125E-2</v>
       </c>
       <c r="J11">
         <v>-0.3076171875</v>
       </c>
       <c r="K11">
-        <v>-0.0054931640625</v>
-      </c>
-    </row>
-    <row r="12">
+        <v>-5.4931640625E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C12">
-        <v>0.03076171875</v>
+        <v>3.076171875E-2</v>
       </c>
       <c r="D12">
         <v>0.62646484375</v>
@@ -920,15 +926,15 @@
         <v>0.230712890625</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C13">
-        <v>0.03173828125</v>
+        <v>3.173828125E-2</v>
       </c>
       <c r="D13">
         <v>0.67431640625</v>
@@ -952,18 +958,18 @@
         <v>-1.8182373046875</v>
       </c>
       <c r="K13">
-        <v>0.0054931640625</v>
-      </c>
-    </row>
-    <row r="14">
+        <v>5.4931640625E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C14">
-        <v>0.00732421875</v>
+        <v>7.32421875E-3</v>
       </c>
       <c r="D14">
         <v>0.5888671875</v>
@@ -990,15 +996,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C15">
-        <v>-0.0146484375</v>
+        <v>-1.46484375E-2</v>
       </c>
       <c r="D15">
         <v>0.5595703125</v>
@@ -1022,18 +1028,18 @@
         <v>0.845947265625</v>
       </c>
       <c r="K15">
-        <v>-0.0823974609375</v>
-      </c>
-    </row>
-    <row r="16">
+        <v>-8.23974609375E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C16">
-        <v>0.00244140625</v>
+        <v>2.44140625E-3</v>
       </c>
       <c r="D16">
         <v>0.4853515625</v>
@@ -1057,18 +1063,18 @@
         <v>-0.1373291015625</v>
       </c>
       <c r="K16">
-        <v>0.010986328125</v>
-      </c>
-    </row>
-    <row r="17">
+        <v>1.0986328125E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C17">
-        <v>0.025390625</v>
+        <v>2.5390625E-2</v>
       </c>
       <c r="D17">
         <v>0.3251953125</v>
@@ -1092,18 +1098,18 @@
         <v>-1.483154296875</v>
       </c>
       <c r="K17">
-        <v>-0.0274658203125</v>
-      </c>
-    </row>
-    <row r="18">
+        <v>-2.74658203125E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B18" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C18">
-        <v>0.00146484375</v>
+        <v>1.46484375E-3</v>
       </c>
       <c r="D18">
         <v>0.21044921875</v>
@@ -1130,18 +1136,18 @@
         <v>-0.252685546875</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C19">
-        <v>0.0185546875</v>
+        <v>1.85546875E-2</v>
       </c>
       <c r="D19">
-        <v>0.08349609375</v>
+        <v>8.349609375E-2</v>
       </c>
       <c r="E19">
         <v>0.99169921875</v>
@@ -1165,18 +1171,18 @@
         <v>0.582275390625</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B20" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C20">
-        <v>-0.0302734375</v>
+        <v>-3.02734375E-2</v>
       </c>
       <c r="D20">
-        <v>0.01123046875</v>
+        <v>1.123046875E-2</v>
       </c>
       <c r="E20">
         <v>0.9990234375</v>
@@ -1200,15 +1206,15 @@
         <v>0.2032470703125</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C21">
-        <v>0.00537109375</v>
+        <v>5.37109375E-3</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -1226,24 +1232,24 @@
         <v>0</v>
       </c>
       <c r="I21">
-        <v>-0.0164794921875</v>
+        <v>-1.64794921875E-2</v>
       </c>
       <c r="J21">
         <v>-0.3076171875</v>
       </c>
       <c r="K21">
-        <v>-0.0054931640625</v>
-      </c>
-    </row>
-    <row r="22">
+        <v>-5.4931640625E-3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C22">
-        <v>0.03125</v>
+        <v>3.125E-2</v>
       </c>
       <c r="D22">
         <v>0.62646484375</v>
@@ -1270,15 +1276,15 @@
         <v>0.230712890625</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C23">
-        <v>0.03173828125</v>
+        <v>3.173828125E-2</v>
       </c>
       <c r="D23">
         <v>0.673828125</v>
@@ -1302,18 +1308,18 @@
         <v>-1.82373046875</v>
       </c>
       <c r="K23">
-        <v>0.0054931640625</v>
-      </c>
-    </row>
-    <row r="24">
+        <v>5.4931640625E-3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C24">
-        <v>0.0078125</v>
+        <v>7.8125E-3</v>
       </c>
       <c r="D24">
         <v>0.5888671875</v>
@@ -1340,15 +1346,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C25">
-        <v>-0.01513671875</v>
+        <v>-1.513671875E-2</v>
       </c>
       <c r="D25">
         <v>0.5595703125</v>
@@ -1372,18 +1378,18 @@
         <v>0.845947265625</v>
       </c>
       <c r="K25">
-        <v>-0.0823974609375</v>
-      </c>
-    </row>
-    <row r="26">
+        <v>-8.23974609375E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C26">
-        <v>0.00244140625</v>
+        <v>2.44140625E-3</v>
       </c>
       <c r="D26">
         <v>0.4853515625</v>
@@ -1407,18 +1413,18 @@
         <v>-0.1318359375</v>
       </c>
       <c r="K26">
-        <v>0.010986328125</v>
-      </c>
-    </row>
-    <row r="27">
+        <v>1.0986328125E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B27" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C27">
-        <v>0.025390625</v>
+        <v>2.5390625E-2</v>
       </c>
       <c r="D27">
         <v>0.32470703125</v>
@@ -1442,18 +1448,18 @@
         <v>-1.483154296875</v>
       </c>
       <c r="K27">
-        <v>-0.0274658203125</v>
-      </c>
-    </row>
-    <row r="28">
+        <v>-2.74658203125E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B28" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C28">
-        <v>0.00146484375</v>
+        <v>1.46484375E-3</v>
       </c>
       <c r="D28">
         <v>0.21044921875</v>
@@ -1480,18 +1486,18 @@
         <v>-0.252685546875</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B29" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C29">
-        <v>0.017578125</v>
+        <v>1.7578125E-2</v>
       </c>
       <c r="D29">
-        <v>0.083984375</v>
+        <v>8.3984375E-2</v>
       </c>
       <c r="E29">
         <v>0.99169921875</v>
@@ -1515,18 +1521,18 @@
         <v>0.582275390625</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B30" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C30">
-        <v>-0.0302734375</v>
+        <v>-3.02734375E-2</v>
       </c>
       <c r="D30">
-        <v>0.01123046875</v>
+        <v>1.123046875E-2</v>
       </c>
       <c r="E30">
         <v>0.9990234375</v>
@@ -1550,15 +1556,15 @@
         <v>0.2032470703125</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B31" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C31">
-        <v>0.00537109375</v>
+        <v>5.37109375E-3</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -1576,24 +1582,24 @@
         <v>0</v>
       </c>
       <c r="I31">
-        <v>-0.0164794921875</v>
+        <v>-1.64794921875E-2</v>
       </c>
       <c r="J31">
         <v>-0.3076171875</v>
       </c>
       <c r="K31">
-        <v>-0.0054931640625</v>
-      </c>
-    </row>
-    <row r="32">
+        <v>-5.4931640625E-3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B32" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C32">
-        <v>0.03076171875</v>
+        <v>3.076171875E-2</v>
       </c>
       <c r="D32">
         <v>0.626953125</v>
@@ -1620,15 +1626,15 @@
         <v>0.230712890625</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B33" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C33">
-        <v>0.03173828125</v>
+        <v>3.173828125E-2</v>
       </c>
       <c r="D33">
         <v>0.6748046875</v>
@@ -1652,18 +1658,18 @@
         <v>-1.8182373046875</v>
       </c>
       <c r="K33">
-        <v>0.0054931640625</v>
-      </c>
-    </row>
-    <row r="34">
+        <v>5.4931640625E-3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B34" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C34">
-        <v>0.00830078125</v>
+        <v>8.30078125E-3</v>
       </c>
       <c r="D34">
         <v>0.5888671875</v>
@@ -1690,15 +1696,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B35" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C35">
-        <v>-0.0146484375</v>
+        <v>-1.46484375E-2</v>
       </c>
       <c r="D35">
         <v>0.55908203125</v>
@@ -1722,18 +1728,18 @@
         <v>0.845947265625</v>
       </c>
       <c r="K35">
-        <v>-0.0823974609375</v>
-      </c>
-    </row>
-    <row r="36">
+        <v>-8.23974609375E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B36" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C36">
-        <v>0.001953125</v>
+        <v>1.953125E-3</v>
       </c>
       <c r="D36">
         <v>0.48583984375</v>
@@ -1757,18 +1763,18 @@
         <v>-0.1318359375</v>
       </c>
       <c r="K36">
-        <v>0.010986328125</v>
-      </c>
-    </row>
-    <row r="37">
+        <v>1.0986328125E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B37" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C37">
-        <v>0.02587890625</v>
+        <v>2.587890625E-2</v>
       </c>
       <c r="D37">
         <v>0.3251953125</v>
@@ -1792,18 +1798,18 @@
         <v>-1.483154296875</v>
       </c>
       <c r="K37">
-        <v>-0.0274658203125</v>
-      </c>
-    </row>
-    <row r="38">
+        <v>-2.74658203125E-2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B38" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C38">
-        <v>0.00146484375</v>
+        <v>1.46484375E-3</v>
       </c>
       <c r="D38">
         <v>0.2099609375</v>
@@ -1830,18 +1836,18 @@
         <v>-0.252685546875</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B39" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C39">
-        <v>0.017578125</v>
+        <v>1.7578125E-2</v>
       </c>
       <c r="D39">
-        <v>0.083984375</v>
+        <v>8.3984375E-2</v>
       </c>
       <c r="E39">
         <v>0.99169921875</v>
@@ -1865,18 +1871,18 @@
         <v>0.582275390625</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B40" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C40">
-        <v>-0.029296875</v>
+        <v>-2.9296875E-2</v>
       </c>
       <c r="D40">
-        <v>0.0107421875</v>
+        <v>1.07421875E-2</v>
       </c>
       <c r="E40">
         <v>1</v>
@@ -1900,15 +1906,15 @@
         <v>0.2032470703125</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B41" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C41">
-        <v>0.00537109375</v>
+        <v>5.37109375E-3</v>
       </c>
       <c r="D41">
         <v>0</v>
@@ -1926,24 +1932,24 @@
         <v>0</v>
       </c>
       <c r="I41">
-        <v>-0.0164794921875</v>
+        <v>-1.64794921875E-2</v>
       </c>
       <c r="J41">
         <v>-0.3021240234375</v>
       </c>
       <c r="K41">
-        <v>-0.0054931640625</v>
-      </c>
-    </row>
-    <row r="42">
+        <v>-5.4931640625E-3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A42" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B42" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C42">
-        <v>0.03076171875</v>
+        <v>3.076171875E-2</v>
       </c>
       <c r="D42">
         <v>0.62646484375</v>
@@ -1970,15 +1976,15 @@
         <v>0.230712890625</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B43" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C43">
-        <v>0.0322265625</v>
+        <v>3.22265625E-2</v>
       </c>
       <c r="D43">
         <v>0.67431640625</v>
@@ -2002,18 +2008,18 @@
         <v>-1.8182373046875</v>
       </c>
       <c r="K43">
-        <v>0.0054931640625</v>
-      </c>
-    </row>
-    <row r="44">
+        <v>5.4931640625E-3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B44" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C44">
-        <v>0.0087890625</v>
+        <v>8.7890625E-3</v>
       </c>
       <c r="D44">
         <v>0.58837890625</v>
@@ -2040,15 +2046,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B45" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C45">
-        <v>-0.01416015625</v>
+        <v>-1.416015625E-2</v>
       </c>
       <c r="D45">
         <v>0.5595703125</v>
@@ -2072,18 +2078,18 @@
         <v>0.845947265625</v>
       </c>
       <c r="K45">
-        <v>-0.0823974609375</v>
-      </c>
-    </row>
-    <row r="46">
+        <v>-8.23974609375E-2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A46" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B46" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C46">
-        <v>0.00244140625</v>
+        <v>2.44140625E-3</v>
       </c>
       <c r="D46">
         <v>0.4853515625</v>
@@ -2107,18 +2113,18 @@
         <v>-0.1373291015625</v>
       </c>
       <c r="K46">
-        <v>0.010986328125</v>
-      </c>
-    </row>
-    <row r="47">
+        <v>1.0986328125E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B47" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C47">
-        <v>0.02587890625</v>
+        <v>2.587890625E-2</v>
       </c>
       <c r="D47">
         <v>0.3251953125</v>
@@ -2142,18 +2148,18 @@
         <v>-1.483154296875</v>
       </c>
       <c r="K47">
-        <v>-0.0274658203125</v>
-      </c>
-    </row>
-    <row r="48">
+        <v>-2.74658203125E-2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B48" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C48">
-        <v>0.00146484375</v>
+        <v>1.46484375E-3</v>
       </c>
       <c r="D48">
         <v>0.2099609375</v>
@@ -2180,18 +2186,18 @@
         <v>-0.252685546875</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A49" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B49" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C49">
-        <v>0.017578125</v>
+        <v>1.7578125E-2</v>
       </c>
       <c r="D49">
-        <v>0.08349609375</v>
+        <v>8.349609375E-2</v>
       </c>
       <c r="E49">
         <v>0.9912109375</v>
@@ -2215,18 +2221,18 @@
         <v>0.582275390625</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A50" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B50" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C50">
-        <v>-0.0302734375</v>
+        <v>-3.02734375E-2</v>
       </c>
       <c r="D50">
-        <v>0.01171875</v>
+        <v>1.171875E-2</v>
       </c>
       <c r="E50">
         <v>0.99951171875</v>
@@ -2250,15 +2256,15 @@
         <v>0.2032470703125</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B51" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C51">
-        <v>0.00537109375</v>
+        <v>5.37109375E-3</v>
       </c>
       <c r="D51">
         <v>0</v>
@@ -2276,24 +2282,24 @@
         <v>0</v>
       </c>
       <c r="I51">
-        <v>-0.0164794921875</v>
+        <v>-1.64794921875E-2</v>
       </c>
       <c r="J51">
         <v>-0.3021240234375</v>
       </c>
       <c r="K51">
-        <v>-0.0054931640625</v>
-      </c>
-    </row>
-    <row r="52">
+        <v>-5.4931640625E-3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A52" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B52" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C52">
-        <v>0.03125</v>
+        <v>3.125E-2</v>
       </c>
       <c r="D52">
         <v>0.62646484375</v>
@@ -2320,15 +2326,15 @@
         <v>0.230712890625</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A53" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B53" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C53">
-        <v>0.03173828125</v>
+        <v>3.173828125E-2</v>
       </c>
       <c r="D53">
         <v>0.673828125</v>
@@ -2352,18 +2358,18 @@
         <v>-1.82373046875</v>
       </c>
       <c r="K53">
-        <v>0.0054931640625</v>
-      </c>
-    </row>
-    <row r="54">
+        <v>5.4931640625E-3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A54" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B54" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C54">
-        <v>0.0078125</v>
+        <v>7.8125E-3</v>
       </c>
       <c r="D54">
         <v>0.587890625</v>
@@ -2390,15 +2396,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A55" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B55" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C55">
-        <v>-0.01513671875</v>
+        <v>-1.513671875E-2</v>
       </c>
       <c r="D55">
         <v>0.5595703125</v>
@@ -2422,18 +2428,18 @@
         <v>0.8404541015625</v>
       </c>
       <c r="K55">
-        <v>-0.0823974609375</v>
-      </c>
-    </row>
-    <row r="56">
+        <v>-8.23974609375E-2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A56" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B56" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C56">
-        <v>0.001953125</v>
+        <v>1.953125E-3</v>
       </c>
       <c r="D56">
         <v>0.48486328125</v>
@@ -2457,18 +2463,18 @@
         <v>-0.1373291015625</v>
       </c>
       <c r="K56">
-        <v>0.010986328125</v>
-      </c>
-    </row>
-    <row r="57">
+        <v>1.0986328125E-2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A57" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B57" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C57">
-        <v>0.02587890625</v>
+        <v>2.587890625E-2</v>
       </c>
       <c r="D57">
         <v>0.3251953125</v>
@@ -2492,18 +2498,18 @@
         <v>-1.483154296875</v>
       </c>
       <c r="K57">
-        <v>-0.0274658203125</v>
-      </c>
-    </row>
-    <row r="58">
+        <v>-2.74658203125E-2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A58" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B58" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C58">
-        <v>0.00146484375</v>
+        <v>1.46484375E-3</v>
       </c>
       <c r="D58">
         <v>0.21044921875</v>
@@ -2530,18 +2536,18 @@
         <v>-0.252685546875</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A59" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B59" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C59">
-        <v>0.01806640625</v>
+        <v>1.806640625E-2</v>
       </c>
       <c r="D59">
-        <v>0.0830078125</v>
+        <v>8.30078125E-2</v>
       </c>
       <c r="E59">
         <v>0.9921875</v>
@@ -2565,18 +2571,18 @@
         <v>0.582275390625</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A60" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B60" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C60">
-        <v>-0.029296875</v>
+        <v>-2.9296875E-2</v>
       </c>
       <c r="D60">
-        <v>0.01171875</v>
+        <v>1.171875E-2</v>
       </c>
       <c r="E60">
         <v>0.9990234375</v>
@@ -2600,15 +2606,15 @@
         <v>0.2032470703125</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A61" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B61" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C61">
-        <v>0.00537109375</v>
+        <v>5.37109375E-3</v>
       </c>
       <c r="D61">
         <v>0</v>
@@ -2626,24 +2632,24 @@
         <v>0</v>
       </c>
       <c r="I61">
-        <v>-0.0164794921875</v>
+        <v>-1.64794921875E-2</v>
       </c>
       <c r="J61">
         <v>-0.3021240234375</v>
       </c>
       <c r="K61">
-        <v>-0.0054931640625</v>
-      </c>
-    </row>
-    <row r="62">
+        <v>-5.4931640625E-3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A62" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B62" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C62">
-        <v>0.03125</v>
+        <v>3.125E-2</v>
       </c>
       <c r="D62">
         <v>0.626953125</v>
@@ -2670,15 +2676,15 @@
         <v>0.230712890625</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A63" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B63" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C63">
-        <v>0.03173828125</v>
+        <v>3.173828125E-2</v>
       </c>
       <c r="D63">
         <v>0.6748046875</v>
@@ -2702,18 +2708,18 @@
         <v>-1.82373046875</v>
       </c>
       <c r="K63">
-        <v>0.0054931640625</v>
-      </c>
-    </row>
-    <row r="64">
+        <v>5.4931640625E-3</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A64" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B64" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C64">
-        <v>0.0078125</v>
+        <v>7.8125E-3</v>
       </c>
       <c r="D64">
         <v>0.58837890625</v>
@@ -2740,15 +2746,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A65" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B65" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C65">
-        <v>-0.0146484375</v>
+        <v>-1.46484375E-2</v>
       </c>
       <c r="D65">
         <v>0.5595703125</v>
@@ -2772,18 +2778,18 @@
         <v>0.8404541015625</v>
       </c>
       <c r="K65">
-        <v>-0.0823974609375</v>
-      </c>
-    </row>
-    <row r="66">
+        <v>-8.23974609375E-2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A66" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B66" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C66">
-        <v>0.001953125</v>
+        <v>1.953125E-3</v>
       </c>
       <c r="D66">
         <v>0.48486328125</v>
@@ -2807,18 +2813,18 @@
         <v>-0.1373291015625</v>
       </c>
       <c r="K66">
-        <v>0.010986328125</v>
-      </c>
-    </row>
-    <row r="67">
+        <v>1.0986328125E-2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A67" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B67" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C67">
-        <v>0.025390625</v>
+        <v>2.5390625E-2</v>
       </c>
       <c r="D67">
         <v>0.32470703125</v>
@@ -2842,18 +2848,18 @@
         <v>-1.483154296875</v>
       </c>
       <c r="K67">
-        <v>-0.0274658203125</v>
-      </c>
-    </row>
-    <row r="68">
+        <v>-2.74658203125E-2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A68" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B68" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C68">
-        <v>0.00146484375</v>
+        <v>1.46484375E-3</v>
       </c>
       <c r="D68">
         <v>0.21044921875</v>
@@ -2880,18 +2886,18 @@
         <v>-0.252685546875</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A69" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B69" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C69">
-        <v>0.01806640625</v>
+        <v>1.806640625E-2</v>
       </c>
       <c r="D69">
-        <v>0.083984375</v>
+        <v>8.3984375E-2</v>
       </c>
       <c r="E69">
         <v>0.99169921875</v>
@@ -2915,18 +2921,18 @@
         <v>0.582275390625</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A70" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B70" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C70">
-        <v>-0.02978515625</v>
+        <v>-2.978515625E-2</v>
       </c>
       <c r="D70">
-        <v>0.01025390625</v>
+        <v>1.025390625E-2</v>
       </c>
       <c r="E70">
         <v>1</v>
@@ -2950,15 +2956,15 @@
         <v>0.2032470703125</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A71" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B71" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C71">
-        <v>0.00537109375</v>
+        <v>5.37109375E-3</v>
       </c>
       <c r="D71">
         <v>0</v>
@@ -2976,24 +2982,24 @@
         <v>0</v>
       </c>
       <c r="I71">
-        <v>-0.010986328125</v>
+        <v>-1.0986328125E-2</v>
       </c>
       <c r="J71">
         <v>-0.3076171875</v>
       </c>
       <c r="K71">
-        <v>-0.0054931640625</v>
-      </c>
-    </row>
-    <row r="72">
+        <v>-5.4931640625E-3</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A72" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B72" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C72">
-        <v>0.03076171875</v>
+        <v>3.076171875E-2</v>
       </c>
       <c r="D72">
         <v>0.626953125</v>
@@ -3020,15 +3026,15 @@
         <v>0.230712890625</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A73" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B73" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C73">
-        <v>0.03173828125</v>
+        <v>3.173828125E-2</v>
       </c>
       <c r="D73">
         <v>0.673828125</v>
@@ -3052,18 +3058,18 @@
         <v>-1.8182373046875</v>
       </c>
       <c r="K73">
-        <v>0.0054931640625</v>
-      </c>
-    </row>
-    <row r="74">
+        <v>5.4931640625E-3</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A74" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B74" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C74">
-        <v>0.0078125</v>
+        <v>7.8125E-3</v>
       </c>
       <c r="D74">
         <v>0.5888671875</v>
@@ -3090,15 +3096,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A75" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B75" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C75">
-        <v>-0.0146484375</v>
+        <v>-1.46484375E-2</v>
       </c>
       <c r="D75">
         <v>0.5595703125</v>
@@ -3122,18 +3128,18 @@
         <v>0.8404541015625</v>
       </c>
       <c r="K75">
-        <v>-0.0823974609375</v>
-      </c>
-    </row>
-    <row r="76">
+        <v>-8.23974609375E-2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A76" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B76" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C76">
-        <v>0.0029296875</v>
+        <v>2.9296875E-3</v>
       </c>
       <c r="D76">
         <v>0.4853515625</v>
@@ -3157,18 +3163,18 @@
         <v>-0.1318359375</v>
       </c>
       <c r="K76">
-        <v>0.010986328125</v>
-      </c>
-    </row>
-    <row r="77">
+        <v>1.0986328125E-2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A77" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B77" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C77">
-        <v>0.025390625</v>
+        <v>2.5390625E-2</v>
       </c>
       <c r="D77">
         <v>0.32421875</v>
@@ -3192,18 +3198,18 @@
         <v>-1.483154296875</v>
       </c>
       <c r="K77">
-        <v>-0.0274658203125</v>
-      </c>
-    </row>
-    <row r="78">
+        <v>-2.74658203125E-2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A78" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B78" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C78">
-        <v>0.001953125</v>
+        <v>1.953125E-3</v>
       </c>
       <c r="D78">
         <v>0.20947265625</v>
@@ -3230,18 +3236,18 @@
         <v>-0.252685546875</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A79" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B79" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C79">
-        <v>0.01806640625</v>
+        <v>1.806640625E-2</v>
       </c>
       <c r="D79">
-        <v>0.08349609375</v>
+        <v>8.349609375E-2</v>
       </c>
       <c r="E79">
         <v>0.99169921875</v>
@@ -3265,18 +3271,18 @@
         <v>0.582275390625</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A80" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B80" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C80">
-        <v>-0.02978515625</v>
+        <v>-2.978515625E-2</v>
       </c>
       <c r="D80">
-        <v>0.0107421875</v>
+        <v>1.07421875E-2</v>
       </c>
       <c r="E80">
         <v>0.9990234375</v>
@@ -3300,15 +3306,15 @@
         <v>0.2032470703125</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A81" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B81" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C81">
-        <v>0.00537109375</v>
+        <v>5.37109375E-3</v>
       </c>
       <c r="D81">
         <v>0</v>
@@ -3326,24 +3332,24 @@
         <v>0</v>
       </c>
       <c r="I81">
-        <v>-0.0164794921875</v>
+        <v>-1.64794921875E-2</v>
       </c>
       <c r="J81">
         <v>-0.3076171875</v>
       </c>
       <c r="K81">
-        <v>-0.0054931640625</v>
-      </c>
-    </row>
-    <row r="82">
+        <v>-5.4931640625E-3</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A82" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B82" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C82">
-        <v>0.03076171875</v>
+        <v>3.076171875E-2</v>
       </c>
       <c r="D82">
         <v>0.62646484375</v>
@@ -3370,15 +3376,15 @@
         <v>0.230712890625</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A83" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B83" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C83">
-        <v>0.0322265625</v>
+        <v>3.22265625E-2</v>
       </c>
       <c r="D83">
         <v>0.6748046875</v>
@@ -3402,18 +3408,18 @@
         <v>-1.8182373046875</v>
       </c>
       <c r="K83">
-        <v>0.0054931640625</v>
-      </c>
-    </row>
-    <row r="84">
+        <v>5.4931640625E-3</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A84" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B84" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C84">
-        <v>0.0078125</v>
+        <v>7.8125E-3</v>
       </c>
       <c r="D84">
         <v>0.5888671875</v>
@@ -3440,15 +3446,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A85" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B85" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C85">
-        <v>-0.0146484375</v>
+        <v>-1.46484375E-2</v>
       </c>
       <c r="D85">
         <v>0.5595703125</v>
@@ -3472,18 +3478,18 @@
         <v>0.845947265625</v>
       </c>
       <c r="K85">
-        <v>-0.0823974609375</v>
-      </c>
-    </row>
-    <row r="86">
+        <v>-8.23974609375E-2</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A86" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B86" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C86">
-        <v>0.00146484375</v>
+        <v>1.46484375E-3</v>
       </c>
       <c r="D86">
         <v>0.4853515625</v>
@@ -3507,18 +3513,18 @@
         <v>-0.1318359375</v>
       </c>
       <c r="K86">
-        <v>0.010986328125</v>
-      </c>
-    </row>
-    <row r="87">
+        <v>1.0986328125E-2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A87" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B87" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C87">
-        <v>0.025390625</v>
+        <v>2.5390625E-2</v>
       </c>
       <c r="D87">
         <v>0.32470703125</v>
@@ -3542,18 +3548,18 @@
         <v>-1.483154296875</v>
       </c>
       <c r="K87">
-        <v>-0.0274658203125</v>
-      </c>
-    </row>
-    <row r="88">
+        <v>-2.74658203125E-2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A88" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B88" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C88">
-        <v>0.001953125</v>
+        <v>1.953125E-3</v>
       </c>
       <c r="D88">
         <v>0.2099609375</v>
@@ -3580,18 +3586,18 @@
         <v>-0.252685546875</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A89" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B89" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C89">
-        <v>0.01806640625</v>
+        <v>1.806640625E-2</v>
       </c>
       <c r="D89">
-        <v>0.083984375</v>
+        <v>8.3984375E-2</v>
       </c>
       <c r="E89">
         <v>0.9912109375</v>
@@ -3615,18 +3621,18 @@
         <v>0.582275390625</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A90" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B90" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C90">
-        <v>-0.02978515625</v>
+        <v>-2.978515625E-2</v>
       </c>
       <c r="D90">
-        <v>0.01123046875</v>
+        <v>1.123046875E-2</v>
       </c>
       <c r="E90">
         <v>0.99951171875</v>
@@ -3650,15 +3656,15 @@
         <v>0.2032470703125</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A91" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B91" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C91">
-        <v>0.00537109375</v>
+        <v>5.37109375E-3</v>
       </c>
       <c r="D91">
         <v>0</v>
@@ -3676,24 +3682,24 @@
         <v>0</v>
       </c>
       <c r="I91">
-        <v>-0.0164794921875</v>
+        <v>-1.64794921875E-2</v>
       </c>
       <c r="J91">
         <v>-0.3076171875</v>
       </c>
       <c r="K91">
-        <v>-0.0054931640625</v>
-      </c>
-    </row>
-    <row r="92">
+        <v>-5.4931640625E-3</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A92" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B92" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C92">
-        <v>0.03076171875</v>
+        <v>3.076171875E-2</v>
       </c>
       <c r="D92">
         <v>0.6259765625</v>
@@ -3720,15 +3726,15 @@
         <v>0.230712890625</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A93" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B93" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C93">
-        <v>0.0322265625</v>
+        <v>3.22265625E-2</v>
       </c>
       <c r="D93">
         <v>0.6748046875</v>
@@ -3752,18 +3758,18 @@
         <v>-1.8182373046875</v>
       </c>
       <c r="K93">
-        <v>0.0054931640625</v>
-      </c>
-    </row>
-    <row r="94">
+        <v>5.4931640625E-3</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A94" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B94" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C94">
-        <v>0.0078125</v>
+        <v>7.8125E-3</v>
       </c>
       <c r="D94">
         <v>0.58837890625</v>
@@ -3790,15 +3796,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A95" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B95" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C95">
-        <v>-0.0146484375</v>
+        <v>-1.46484375E-2</v>
       </c>
       <c r="D95">
         <v>0.5595703125</v>
@@ -3822,18 +3828,18 @@
         <v>0.845947265625</v>
       </c>
       <c r="K95">
-        <v>-0.0823974609375</v>
-      </c>
-    </row>
-    <row r="96">
+        <v>-8.23974609375E-2</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A96" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B96" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C96">
-        <v>0.00244140625</v>
+        <v>2.44140625E-3</v>
       </c>
       <c r="D96">
         <v>0.4853515625</v>
@@ -3857,18 +3863,18 @@
         <v>-0.1318359375</v>
       </c>
       <c r="K96">
-        <v>0.010986328125</v>
-      </c>
-    </row>
-    <row r="97">
+        <v>1.0986328125E-2</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A97" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B97" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C97">
-        <v>0.02587890625</v>
+        <v>2.587890625E-2</v>
       </c>
       <c r="D97">
         <v>0.32470703125</v>
@@ -3892,18 +3898,18 @@
         <v>-1.483154296875</v>
       </c>
       <c r="K97">
-        <v>-0.0274658203125</v>
-      </c>
-    </row>
-    <row r="98">
+        <v>-2.74658203125E-2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A98" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B98" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C98">
-        <v>0.00146484375</v>
+        <v>1.46484375E-3</v>
       </c>
       <c r="D98">
         <v>0.21044921875</v>
@@ -3930,18 +3936,18 @@
         <v>-0.252685546875</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A99" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B99" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C99">
-        <v>0.01806640625</v>
+        <v>1.806640625E-2</v>
       </c>
       <c r="D99">
-        <v>0.083984375</v>
+        <v>8.3984375E-2</v>
       </c>
       <c r="E99">
         <v>0.9912109375</v>
@@ -3965,18 +3971,18 @@
         <v>0.582275390625</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A100" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B100" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C100">
-        <v>0.01806640625</v>
+        <v>1.806640625E-2</v>
       </c>
       <c r="D100">
-        <v>0.083984375</v>
+        <v>8.3984375E-2</v>
       </c>
       <c r="E100">
         <v>0.9912109375</v>
@@ -4000,15 +4006,15 @@
         <v>0.582275390625</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A101" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B101" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C101">
-        <v>0.0048828125</v>
+        <v>4.8828125E-3</v>
       </c>
       <c r="D101">
         <v>0</v>
@@ -4026,24 +4032,24 @@
         <v>0</v>
       </c>
       <c r="I101">
-        <v>-0.0164794921875</v>
+        <v>-1.64794921875E-2</v>
       </c>
       <c r="J101">
         <v>-0.3076171875</v>
       </c>
       <c r="K101">
-        <v>-0.0054931640625</v>
-      </c>
-    </row>
-    <row r="102">
+        <v>-5.4931640625E-3</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A102" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B102" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C102">
-        <v>0.03076171875</v>
+        <v>3.076171875E-2</v>
       </c>
       <c r="D102">
         <v>0.6259765625</v>
@@ -4070,15 +4076,15 @@
         <v>0.230712890625</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A103" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B103" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C103">
-        <v>0.03173828125</v>
+        <v>3.173828125E-2</v>
       </c>
       <c r="D103">
         <v>0.673828125</v>
@@ -4102,18 +4108,18 @@
         <v>-1.82373046875</v>
       </c>
       <c r="K103">
-        <v>0.0054931640625</v>
-      </c>
-    </row>
-    <row r="104">
+        <v>5.4931640625E-3</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A104" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B104" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C104">
-        <v>0.00830078125</v>
+        <v>8.30078125E-3</v>
       </c>
       <c r="D104">
         <v>0.5888671875</v>
@@ -4140,15 +4146,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A105" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B105" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C105">
-        <v>-0.01513671875</v>
+        <v>-1.513671875E-2</v>
       </c>
       <c r="D105">
         <v>0.5595703125</v>
@@ -4172,18 +4178,18 @@
         <v>0.845947265625</v>
       </c>
       <c r="K105">
-        <v>-0.0823974609375</v>
-      </c>
-    </row>
-    <row r="106">
+        <v>-8.23974609375E-2</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A106" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B106" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C106">
-        <v>0.001953125</v>
+        <v>1.953125E-3</v>
       </c>
       <c r="D106">
         <v>0.48583984375</v>
@@ -4207,18 +4213,18 @@
         <v>-0.1318359375</v>
       </c>
       <c r="K106">
-        <v>0.010986328125</v>
-      </c>
-    </row>
-    <row r="107">
+        <v>1.0986328125E-2</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A107" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B107" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C107">
-        <v>0.02490234375</v>
+        <v>2.490234375E-2</v>
       </c>
       <c r="D107">
         <v>0.32470703125</v>
@@ -4242,18 +4248,18 @@
         <v>-1.483154296875</v>
       </c>
       <c r="K107">
-        <v>-0.0274658203125</v>
-      </c>
-    </row>
-    <row r="108">
+        <v>-2.74658203125E-2</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A108" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B108" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C108">
-        <v>0.001953125</v>
+        <v>1.953125E-3</v>
       </c>
       <c r="D108">
         <v>0.2099609375</v>
@@ -4280,18 +4286,18 @@
         <v>-0.252685546875</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A109" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B109" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C109">
-        <v>0.0185546875</v>
+        <v>1.85546875E-2</v>
       </c>
       <c r="D109">
-        <v>0.083984375</v>
+        <v>8.3984375E-2</v>
       </c>
       <c r="E109">
         <v>0.99169921875</v>
@@ -4315,18 +4321,18 @@
         <v>0.582275390625</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A110" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B110" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C110">
-        <v>-0.0302734375</v>
+        <v>-3.02734375E-2</v>
       </c>
       <c r="D110">
-        <v>0.0107421875</v>
+        <v>1.07421875E-2</v>
       </c>
       <c r="E110">
         <v>0.9990234375</v>
@@ -4350,15 +4356,15 @@
         <v>0.2032470703125</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A111" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B111" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C111">
-        <v>0.00537109375</v>
+        <v>5.37109375E-3</v>
       </c>
       <c r="D111">
         <v>0</v>
@@ -4376,24 +4382,24 @@
         <v>0</v>
       </c>
       <c r="I111">
-        <v>-0.02197265625</v>
+        <v>-2.197265625E-2</v>
       </c>
       <c r="J111">
         <v>-0.3076171875</v>
       </c>
       <c r="K111">
-        <v>-0.0054931640625</v>
-      </c>
-    </row>
-    <row r="112">
+        <v>-5.4931640625E-3</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A112" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B112" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C112">
-        <v>0.03125</v>
+        <v>3.125E-2</v>
       </c>
       <c r="D112">
         <v>0.62646484375</v>
@@ -4420,15 +4426,15 @@
         <v>0.230712890625</v>
       </c>
     </row>
-    <row r="113">
+    <row r="113" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A113" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B113" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C113">
-        <v>0.03125</v>
+        <v>3.125E-2</v>
       </c>
       <c r="D113">
         <v>0.673828125</v>
@@ -4452,18 +4458,18 @@
         <v>-1.82373046875</v>
       </c>
       <c r="K113">
-        <v>0.0054931640625</v>
-      </c>
-    </row>
-    <row r="114">
+        <v>5.4931640625E-3</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A114" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B114" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C114">
-        <v>0.0078125</v>
+        <v>7.8125E-3</v>
       </c>
       <c r="D114">
         <v>0.58837890625</v>
@@ -4490,15 +4496,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A115" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B115" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C115">
-        <v>-0.0146484375</v>
+        <v>-1.46484375E-2</v>
       </c>
       <c r="D115">
         <v>0.55908203125</v>
@@ -4522,18 +4528,18 @@
         <v>0.845947265625</v>
       </c>
       <c r="K115">
-        <v>-0.0823974609375</v>
-      </c>
-    </row>
-    <row r="116">
+        <v>-8.23974609375E-2</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A116" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B116" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C116">
-        <v>0.00244140625</v>
+        <v>2.44140625E-3</v>
       </c>
       <c r="D116">
         <v>0.4853515625</v>
@@ -4557,18 +4563,18 @@
         <v>-0.1318359375</v>
       </c>
       <c r="K116">
-        <v>0.010986328125</v>
-      </c>
-    </row>
-    <row r="117">
+        <v>1.0986328125E-2</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A117" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B117" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C117">
-        <v>0.02490234375</v>
+        <v>2.490234375E-2</v>
       </c>
       <c r="D117">
         <v>0.32470703125</v>
@@ -4592,18 +4598,18 @@
         <v>-1.4886474609375</v>
       </c>
       <c r="K117">
-        <v>-0.0274658203125</v>
-      </c>
-    </row>
-    <row r="118">
+        <v>-2.74658203125E-2</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A118" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B118" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C118">
-        <v>0.001953125</v>
+        <v>1.953125E-3</v>
       </c>
       <c r="D118">
         <v>0.2109375</v>
@@ -4630,18 +4636,18 @@
         <v>-0.252685546875</v>
       </c>
     </row>
-    <row r="119">
+    <row r="119" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A119" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B119" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C119">
-        <v>0.0185546875</v>
+        <v>1.85546875E-2</v>
       </c>
       <c r="D119">
-        <v>0.083984375</v>
+        <v>8.3984375E-2</v>
       </c>
       <c r="E119">
         <v>0.99169921875</v>
@@ -4665,18 +4671,18 @@
         <v>0.582275390625</v>
       </c>
     </row>
-    <row r="120">
+    <row r="120" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A120" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B120" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C120">
-        <v>-0.0302734375</v>
+        <v>-3.02734375E-2</v>
       </c>
       <c r="D120">
-        <v>0.0107421875</v>
+        <v>1.07421875E-2</v>
       </c>
       <c r="E120">
         <v>0.9990234375</v>
@@ -4700,15 +4706,15 @@
         <v>0.2032470703125</v>
       </c>
     </row>
-    <row r="121">
+    <row r="121" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A121" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B121" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C121">
-        <v>0.00537109375</v>
+        <v>5.37109375E-3</v>
       </c>
       <c r="D121">
         <v>0</v>
@@ -4726,24 +4732,24 @@
         <v>0</v>
       </c>
       <c r="I121">
-        <v>-0.02197265625</v>
+        <v>-2.197265625E-2</v>
       </c>
       <c r="J121">
         <v>-0.3076171875</v>
       </c>
       <c r="K121">
-        <v>-0.0054931640625</v>
-      </c>
-    </row>
-    <row r="122">
+        <v>-5.4931640625E-3</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A122" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B122" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C122">
-        <v>0.03125</v>
+        <v>3.125E-2</v>
       </c>
       <c r="D122">
         <v>0.62646484375</v>
@@ -4770,15 +4776,15 @@
         <v>0.230712890625</v>
       </c>
     </row>
-    <row r="123">
+    <row r="123" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A123" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B123" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C123">
-        <v>0.03125</v>
+        <v>3.125E-2</v>
       </c>
       <c r="D123">
         <v>0.673828125</v>
@@ -4802,18 +4808,18 @@
         <v>-1.8182373046875</v>
       </c>
       <c r="K123">
-        <v>0.0054931640625</v>
-      </c>
-    </row>
-    <row r="124">
+        <v>5.4931640625E-3</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A124" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B124" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C124">
-        <v>0.00830078125</v>
+        <v>8.30078125E-3</v>
       </c>
       <c r="D124">
         <v>0.5888671875</v>
@@ -4840,15 +4846,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125">
+    <row r="125" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A125" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B125" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C125">
-        <v>-0.0146484375</v>
+        <v>-1.46484375E-2</v>
       </c>
       <c r="D125">
         <v>0.5595703125</v>
@@ -4872,18 +4878,18 @@
         <v>0.845947265625</v>
       </c>
       <c r="K125">
-        <v>-0.0823974609375</v>
-      </c>
-    </row>
-    <row r="126">
+        <v>-8.23974609375E-2</v>
+      </c>
+    </row>
+    <row r="126" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A126" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B126" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C126">
-        <v>0.001953125</v>
+        <v>1.953125E-3</v>
       </c>
       <c r="D126">
         <v>0.4853515625</v>
@@ -4907,18 +4913,18 @@
         <v>-0.1263427734375</v>
       </c>
       <c r="K126">
-        <v>0.010986328125</v>
-      </c>
-    </row>
-    <row r="127">
+        <v>1.0986328125E-2</v>
+      </c>
+    </row>
+    <row r="127" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A127" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B127" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C127">
-        <v>0.025390625</v>
+        <v>2.5390625E-2</v>
       </c>
       <c r="D127">
         <v>0.32470703125</v>
@@ -4942,18 +4948,18 @@
         <v>-1.4886474609375</v>
       </c>
       <c r="K127">
-        <v>-0.0274658203125</v>
-      </c>
-    </row>
-    <row r="128">
+        <v>-2.74658203125E-2</v>
+      </c>
+    </row>
+    <row r="128" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A128" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B128" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C128">
-        <v>0.001953125</v>
+        <v>1.953125E-3</v>
       </c>
       <c r="D128">
         <v>0.21044921875</v>
@@ -4980,18 +4986,18 @@
         <v>-0.252685546875</v>
       </c>
     </row>
-    <row r="129">
+    <row r="129" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A129" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B129" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C129">
-        <v>0.0185546875</v>
+        <v>1.85546875E-2</v>
       </c>
       <c r="D129">
-        <v>0.083984375</v>
+        <v>8.3984375E-2</v>
       </c>
       <c r="E129">
         <v>0.99169921875</v>
@@ -5015,18 +5021,18 @@
         <v>0.582275390625</v>
       </c>
     </row>
-    <row r="130">
+    <row r="130" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A130" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B130" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C130">
-        <v>-0.02978515625</v>
+        <v>-2.978515625E-2</v>
       </c>
       <c r="D130">
-        <v>0.01123046875</v>
+        <v>1.123046875E-2</v>
       </c>
       <c r="E130">
         <v>1</v>
@@ -5050,18 +5056,18 @@
         <v>0.2032470703125</v>
       </c>
     </row>
-    <row r="131">
+    <row r="131" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A131" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B131" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C131">
-        <v>0.00537109375</v>
+        <v>5.37109375E-3</v>
       </c>
       <c r="D131">
-        <v>-0.00048828125</v>
+        <v>-4.8828125E-4</v>
       </c>
       <c r="E131">
         <v>1.00341796875</v>
@@ -5076,24 +5082,24 @@
         <v>0</v>
       </c>
       <c r="I131">
-        <v>-0.02197265625</v>
+        <v>-2.197265625E-2</v>
       </c>
       <c r="J131">
         <v>-0.3076171875</v>
       </c>
       <c r="K131">
-        <v>-0.0054931640625</v>
-      </c>
-    </row>
-    <row r="132">
+        <v>-5.4931640625E-3</v>
+      </c>
+    </row>
+    <row r="132" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A132" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B132" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C132">
-        <v>0.03076171875</v>
+        <v>3.076171875E-2</v>
       </c>
       <c r="D132">
         <v>0.62646484375</v>
@@ -5120,15 +5126,15 @@
         <v>0.230712890625</v>
       </c>
     </row>
-    <row r="133">
+    <row r="133" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A133" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B133" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C133">
-        <v>0.0322265625</v>
+        <v>3.22265625E-2</v>
       </c>
       <c r="D133">
         <v>0.673828125</v>
@@ -5152,18 +5158,18 @@
         <v>-1.8182373046875</v>
       </c>
       <c r="K133">
-        <v>0.0054931640625</v>
-      </c>
-    </row>
-    <row r="134">
+        <v>5.4931640625E-3</v>
+      </c>
+    </row>
+    <row r="134" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A134" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B134" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C134">
-        <v>0.00830078125</v>
+        <v>8.30078125E-3</v>
       </c>
       <c r="D134">
         <v>0.58935546875</v>
@@ -5190,15 +5196,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135">
+    <row r="135" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A135" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B135" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C135">
-        <v>-0.0146484375</v>
+        <v>-1.46484375E-2</v>
       </c>
       <c r="D135">
         <v>0.5595703125</v>
@@ -5222,18 +5228,18 @@
         <v>0.845947265625</v>
       </c>
       <c r="K135">
-        <v>-0.0823974609375</v>
-      </c>
-    </row>
-    <row r="136">
+        <v>-8.23974609375E-2</v>
+      </c>
+    </row>
+    <row r="136" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A136" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B136" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C136">
-        <v>0.00146484375</v>
+        <v>1.46484375E-3</v>
       </c>
       <c r="D136">
         <v>0.48486328125</v>
@@ -5257,18 +5263,18 @@
         <v>-0.1263427734375</v>
       </c>
       <c r="K136">
-        <v>0.010986328125</v>
-      </c>
-    </row>
-    <row r="137">
+        <v>1.0986328125E-2</v>
+      </c>
+    </row>
+    <row r="137" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A137" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B137" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C137">
-        <v>0.025390625</v>
+        <v>2.5390625E-2</v>
       </c>
       <c r="D137">
         <v>0.32470703125</v>
@@ -5292,18 +5298,18 @@
         <v>-1.4886474609375</v>
       </c>
       <c r="K137">
-        <v>-0.0274658203125</v>
-      </c>
-    </row>
-    <row r="138">
+        <v>-2.74658203125E-2</v>
+      </c>
+    </row>
+    <row r="138" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A138" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B138" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C138">
-        <v>0.001953125</v>
+        <v>1.953125E-3</v>
       </c>
       <c r="D138">
         <v>0.21044921875</v>
@@ -5330,18 +5336,18 @@
         <v>-0.252685546875</v>
       </c>
     </row>
-    <row r="139">
+    <row r="139" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A139" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B139" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C139">
-        <v>0.0185546875</v>
+        <v>1.85546875E-2</v>
       </c>
       <c r="D139">
-        <v>0.083984375</v>
+        <v>8.3984375E-2</v>
       </c>
       <c r="E139">
         <v>0.99169921875</v>
@@ -5365,18 +5371,18 @@
         <v>0.582275390625</v>
       </c>
     </row>
-    <row r="140">
+    <row r="140" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A140" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B140" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C140">
-        <v>-0.029296875</v>
+        <v>-2.9296875E-2</v>
       </c>
       <c r="D140">
-        <v>0.0107421875</v>
+        <v>1.07421875E-2</v>
       </c>
       <c r="E140">
         <v>0.99951171875</v>
@@ -5400,18 +5406,18 @@
         <v>0.2032470703125</v>
       </c>
     </row>
-    <row r="141">
+    <row r="141" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A141" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B141" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C141">
-        <v>0.0048828125</v>
+        <v>4.8828125E-3</v>
       </c>
       <c r="D141">
-        <v>-0.00048828125</v>
+        <v>-4.8828125E-4</v>
       </c>
       <c r="E141">
         <v>1.0029296875</v>
@@ -5426,24 +5432,24 @@
         <v>0</v>
       </c>
       <c r="I141">
-        <v>-0.0164794921875</v>
+        <v>-1.64794921875E-2</v>
       </c>
       <c r="J141">
         <v>-0.3076171875</v>
       </c>
       <c r="K141">
-        <v>-0.0054931640625</v>
-      </c>
-    </row>
-    <row r="142">
+        <v>-5.4931640625E-3</v>
+      </c>
+    </row>
+    <row r="142" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A142" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B142" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C142">
-        <v>0.03076171875</v>
+        <v>3.076171875E-2</v>
       </c>
       <c r="D142">
         <v>0.62646484375</v>
@@ -5470,15 +5476,15 @@
         <v>0.230712890625</v>
       </c>
     </row>
-    <row r="143">
+    <row r="143" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A143" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B143" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C143">
-        <v>0.0322265625</v>
+        <v>3.22265625E-2</v>
       </c>
       <c r="D143">
         <v>0.673828125</v>
@@ -5502,18 +5508,18 @@
         <v>-1.8182373046875</v>
       </c>
       <c r="K143">
-        <v>0.0054931640625</v>
-      </c>
-    </row>
-    <row r="144">
+        <v>5.4931640625E-3</v>
+      </c>
+    </row>
+    <row r="144" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A144" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B144" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C144">
-        <v>0.00830078125</v>
+        <v>8.30078125E-3</v>
       </c>
       <c r="D144">
         <v>0.58837890625</v>
@@ -5540,15 +5546,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145">
+    <row r="145" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A145" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B145" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C145">
-        <v>-0.01513671875</v>
+        <v>-1.513671875E-2</v>
       </c>
       <c r="D145">
         <v>0.5595703125</v>
@@ -5572,18 +5578,18 @@
         <v>0.845947265625</v>
       </c>
       <c r="K145">
-        <v>-0.0823974609375</v>
-      </c>
-    </row>
-    <row r="146">
+        <v>-8.23974609375E-2</v>
+      </c>
+    </row>
+    <row r="146" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A146" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B146" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C146">
-        <v>0.00146484375</v>
+        <v>1.46484375E-3</v>
       </c>
       <c r="D146">
         <v>0.48486328125</v>
@@ -5607,18 +5613,18 @@
         <v>-0.1263427734375</v>
       </c>
       <c r="K146">
-        <v>0.010986328125</v>
-      </c>
-    </row>
-    <row r="147">
+        <v>1.0986328125E-2</v>
+      </c>
+    </row>
+    <row r="147" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A147" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B147" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C147">
-        <v>0.025390625</v>
+        <v>2.5390625E-2</v>
       </c>
       <c r="D147">
         <v>0.32470703125</v>
@@ -5642,18 +5648,18 @@
         <v>-1.4886474609375</v>
       </c>
       <c r="K147">
-        <v>-0.0274658203125</v>
-      </c>
-    </row>
-    <row r="148">
+        <v>-2.74658203125E-2</v>
+      </c>
+    </row>
+    <row r="148" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A148" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B148" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C148">
-        <v>0.00146484375</v>
+        <v>1.46484375E-3</v>
       </c>
       <c r="D148">
         <v>0.2099609375</v>
@@ -5680,18 +5686,18 @@
         <v>-0.252685546875</v>
       </c>
     </row>
-    <row r="149">
+    <row r="149" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A149" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B149" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C149">
-        <v>0.01806640625</v>
+        <v>1.806640625E-2</v>
       </c>
       <c r="D149">
-        <v>0.08447265625</v>
+        <v>8.447265625E-2</v>
       </c>
       <c r="E149">
         <v>0.9912109375</v>
@@ -5715,18 +5721,18 @@
         <v>0.582275390625</v>
       </c>
     </row>
-    <row r="150">
+    <row r="150" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A150" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B150" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C150">
-        <v>-0.029296875</v>
+        <v>-2.9296875E-2</v>
       </c>
       <c r="D150">
-        <v>0.01123046875</v>
+        <v>1.123046875E-2</v>
       </c>
       <c r="E150">
         <v>1</v>
@@ -5750,18 +5756,18 @@
         <v>0.2032470703125</v>
       </c>
     </row>
-    <row r="151">
+    <row r="151" spans="1:11" hidden="1" x14ac:dyDescent="0.4">
       <c r="A151" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B151" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C151">
-        <v>0.0048828125</v>
+        <v>4.8828125E-3</v>
       </c>
       <c r="D151">
-        <v>-0.00048828125</v>
+        <v>-4.8828125E-4</v>
       </c>
       <c r="E151">
         <v>1.00244140625</v>
@@ -5776,16 +5782,24 @@
         <v>0</v>
       </c>
       <c r="I151">
-        <v>-0.0164794921875</v>
+        <v>-1.64794921875E-2</v>
       </c>
       <c r="J151">
         <v>-0.3076171875</v>
       </c>
       <c r="K151">
-        <v>-0.0054931640625</v>
+        <v>-5.4931640625E-3</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:K151" xr:uid="{049FB1B4-2A61-4643-8816-8B76EC36FD4B}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="0x01"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>